--- a/assessment_forms/013_university_faculty_research_impact_assessment--assessment_forms.xlsx
+++ b/assessment_forms/013_university_faculty_research_impact_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Research Impact</t>
+          <t>Research Impact Question10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
